--- a/docs/plc_log_lists.xlsx
+++ b/docs/plc_log_lists.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\e_pcmaster_elecroomscada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\e_pcmaster_elecroomscada\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7E3332-1310-4E8F-9900-7DC89E5FD084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40DEA7D-ED98-4222-B04B-FD319D1057CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25290" yWindow="2415" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="-1395" yWindow="1350" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="1012">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -3406,14 +3406,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7049,7 +7049,7 @@
       <c r="L2" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="15" t="s">
         <v>956</v>
       </c>
       <c r="O2" s="6" t="s">
@@ -7099,7 +7099,7 @@
       <c r="L3" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="M3" s="13"/>
+      <c r="M3" s="15"/>
       <c r="O3" s="6" t="s">
         <v>293</v>
       </c>
@@ -7132,7 +7132,7 @@
       <c r="L4" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="15"/>
       <c r="O4" s="6" t="s">
         <v>920</v>
       </c>
@@ -7165,7 +7165,7 @@
       <c r="L5" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="M5" s="13"/>
+      <c r="M5" s="15"/>
       <c r="O5" s="6" t="s">
         <v>921</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="L6" s="10" t="s">
         <v>899</v>
       </c>
-      <c r="M6" s="13"/>
+      <c r="M6" s="15"/>
       <c r="O6" s="10" t="s">
         <v>922</v>
       </c>
@@ -7247,7 +7247,7 @@
       <c r="L7" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="15"/>
       <c r="O7" s="8" t="s">
         <v>450</v>
       </c>
@@ -7292,7 +7292,7 @@
       <c r="L8" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="M8" s="13"/>
+      <c r="M8" s="15"/>
       <c r="O8" s="8" t="s">
         <v>557</v>
       </c>
@@ -7335,7 +7335,7 @@
       <c r="L9" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="M9" s="13"/>
+      <c r="M9" s="15"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -7371,7 +7371,7 @@
       <c r="L10" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="M10" s="13"/>
+      <c r="M10" s="15"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -7407,7 +7407,7 @@
       <c r="L11" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M11" s="13"/>
+      <c r="M11" s="15"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -7443,7 +7443,7 @@
       <c r="L12" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="M12" s="13"/>
+      <c r="M12" s="15"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -7479,7 +7479,7 @@
       <c r="L13" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="M13" s="13"/>
+      <c r="M13" s="15"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -7515,7 +7515,7 @@
       <c r="L14" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="M14" s="13"/>
+      <c r="M14" s="15"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
@@ -7549,7 +7549,7 @@
       <c r="L15" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="M15" s="13"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -7585,7 +7585,7 @@
       <c r="L16" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="M16" s="13"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -7624,7 +7624,7 @@
       <c r="L17" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="M17" s="13"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -7660,7 +7660,7 @@
       <c r="L18" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="M18" s="13"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -7698,14 +7698,26 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="J20" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="J21" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -8426,10 +8438,10 @@
       <c r="J43" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="K43" s="14" t="s">
+      <c r="K43" s="13" t="s">
         <v>911</v>
       </c>
-      <c r="L43" s="14" t="s">
+      <c r="L43" s="13" t="s">
         <v>1002</v>
       </c>
       <c r="M43" s="3" t="s">
@@ -8440,13 +8452,13 @@
       <c r="J44" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="K44" s="14" t="s">
+      <c r="K44" s="13" t="s">
         <v>911</v>
       </c>
-      <c r="L44" s="14" t="s">
+      <c r="L44" s="13" t="s">
         <v>1003</v>
       </c>
-      <c r="M44" s="15" t="s">
+      <c r="M44" s="14" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -8520,7 +8532,7 @@
         <v>888</v>
       </c>
       <c r="L49" s="6"/>
-      <c r="M49" s="13" t="s">
+      <c r="M49" s="15" t="s">
         <v>894</v>
       </c>
     </row>
@@ -8556,7 +8568,7 @@
         <v>889</v>
       </c>
       <c r="L50" s="6"/>
-      <c r="M50" s="13"/>
+      <c r="M50" s="15"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -8590,7 +8602,7 @@
         <v>890</v>
       </c>
       <c r="L51" s="6"/>
-      <c r="M51" s="13"/>
+      <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -8624,7 +8636,7 @@
         <v>891</v>
       </c>
       <c r="L52" s="6"/>
-      <c r="M52" s="13"/>
+      <c r="M52" s="15"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -8658,7 +8670,7 @@
         <v>892</v>
       </c>
       <c r="L53" s="6"/>
-      <c r="M53" s="13"/>
+      <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -8692,7 +8704,7 @@
         <v>893</v>
       </c>
       <c r="L54" s="6"/>
-      <c r="M54" s="13"/>
+      <c r="M54" s="15"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
@@ -8724,7 +8736,7 @@
         <v>966</v>
       </c>
       <c r="L55" s="6"/>
-      <c r="M55" s="13"/>
+      <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
@@ -8756,7 +8768,7 @@
         <v>967</v>
       </c>
       <c r="L56" s="6"/>
-      <c r="M56" s="13"/>
+      <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
@@ -8788,7 +8800,7 @@
         <v>968</v>
       </c>
       <c r="L57" s="6"/>
-      <c r="M57" s="13"/>
+      <c r="M57" s="15"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
@@ -8820,7 +8832,7 @@
         <v>969</v>
       </c>
       <c r="L58" s="6"/>
-      <c r="M58" s="13"/>
+      <c r="M58" s="15"/>
     </row>
     <row r="59" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -8854,7 +8866,7 @@
         <v>970</v>
       </c>
       <c r="L59" s="8"/>
-      <c r="M59" s="13"/>
+      <c r="M59" s="15"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -8888,7 +8900,7 @@
         <v>971</v>
       </c>
       <c r="L60" s="8"/>
-      <c r="M60" s="13" t="s">
+      <c r="M60" s="15" t="s">
         <v>953</v>
       </c>
     </row>
@@ -8924,7 +8936,7 @@
         <v>972</v>
       </c>
       <c r="L61" s="8"/>
-      <c r="M61" s="13"/>
+      <c r="M61" s="15"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -8958,7 +8970,7 @@
         <v>973</v>
       </c>
       <c r="L62" s="8"/>
-      <c r="M62" s="13"/>
+      <c r="M62" s="15"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -8994,7 +9006,7 @@
       <c r="L63" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="M63" s="13"/>
+      <c r="M63" s="15"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -9030,7 +9042,7 @@
       <c r="L64" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="M64" s="13"/>
+      <c r="M64" s="15"/>
     </row>
     <row r="65" spans="1:13" ht="82.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -9066,7 +9078,7 @@
       <c r="L65" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="M65" s="13"/>
+      <c r="M65" s="15"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">

--- a/docs/plc_log_lists.xlsx
+++ b/docs/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\e_pcmaster_elecroomscada\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40DEA7D-ED98-4222-B04B-FD319D1057CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EF3CB1-D623-4481-A595-A3B399105C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1395" yWindow="1350" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="-27210" yWindow="1710" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="1016">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -3254,6 +3254,20 @@
   <si>
     <t>PLC_to_PC_heart_bit</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어컨01 운전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어컨02 운전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00957</t>
+  </si>
+  <si>
+    <t>D00958</t>
   </si>
 </sst>
 </file>
@@ -9084,6 +9098,20 @@
       <c r="A66" t="s">
         <v>954</v>
       </c>
+      <c r="J66" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J67" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>1015</v>
+      </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
